--- a/experiments/MC_DATASET/model.xlsx
+++ b/experiments/MC_DATASET/model.xlsx
@@ -9,13 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19935" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="MODEL" sheetId="1" r:id="rId1"/>
     <sheet name="TRACK" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MODEL!$E$1:$K$40</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -81,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="224">
   <si>
     <t>MODEL_TAG</t>
   </si>
@@ -158,18 +161,10 @@
     <t>msr_radarpillar</t>
   </si>
   <si>
-    <t xml:space="preserve"> trained</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>基模</t>
-    </r>
+    <t>trained</t>
+  </si>
+  <si>
+    <t>基模</t>
   </si>
   <si>
     <t>[x,y,z,dop_x_gnd,dop_y_gnd,rcs]</t>
@@ -193,7 +188,7 @@
     <t>NMS[gpu,0.1,mc]</t>
   </si>
   <si>
-    <t>5.597G</t>
+    <t>0.738G</t>
   </si>
   <si>
     <t>0.187M</t>
@@ -205,24 +200,13 @@
     <t>msr_centerhead2d</t>
   </si>
   <si>
-    <r>
-      <t>2danchorfree</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是否有增益</t>
-    </r>
+    <t>2danchorfree是否有增益</t>
   </si>
   <si>
     <t>anchorfree</t>
   </si>
   <si>
-    <t>9.214G</t>
+    <t>2.336G</t>
   </si>
   <si>
     <t>0.387M</t>
@@ -231,24 +215,13 @@
     <t>msr_centerhead3d</t>
   </si>
   <si>
-    <r>
-      <t>3danchorfree</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是否有增益</t>
-    </r>
+    <t>3danchorfree是否有增益</t>
   </si>
   <si>
     <t>anchorfree3d</t>
   </si>
   <si>
-    <t>20.835G</t>
+    <t>2.642G</t>
   </si>
   <si>
     <t>0.425M</t>
@@ -257,44 +230,22 @@
     <t>msr_head2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>多头注意力是否有增益</t>
-    </r>
+    <t>多头注意力是否有增益</t>
   </si>
   <si>
     <t>PAtt[head:2]</t>
   </si>
   <si>
-    <t>5.598G</t>
-  </si>
-  <si>
     <t>msr_repdwc32</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">repdwc32 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是否能够有增益</t>
-    </r>
+    <t>repdwc32 是否能够有增益</t>
   </si>
   <si>
     <t>RepDwc[3,5,5]*[32,32,32]</t>
   </si>
   <si>
-    <t>2.653G</t>
+    <t>0.370G</t>
   </si>
   <si>
     <t>0.060M</t>
@@ -303,18 +254,7 @@
     <t>msr_repdwc64</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">repdwc64 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是否能够有增益</t>
-    </r>
+    <t>repdwc64 是否能够有增益</t>
   </si>
   <si>
     <t>RepDwc[3,5,5]*[64,64,64]</t>
@@ -323,7 +263,7 @@
     <t>UPSAMPLE[1,2,4]+CONCAT[192]</t>
   </si>
   <si>
-    <t>4.235G</t>
+    <t>1.091G</t>
   </si>
   <si>
     <t>0.180M</t>
@@ -332,36 +272,16 @@
     <t>msr_centerhead3d_k1</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">centerhe3d-variant
+    <t>centerhe3d-variant
 1. shared_conv 96→64 3×3
 2. SepHead×5
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(64→64 1×1) + 1 final(64→C 1×1)</t>
-    </r>
+3. 每头 1 hidden(64→64 1×1) + 1 final(64→C 1×1)</t>
   </si>
   <si>
     <t>anchorfree3d-varant</t>
   </si>
   <si>
-    <t>5.000G</t>
+    <t>1.282G</t>
   </si>
   <si>
     <t>0.255M</t>
@@ -370,69 +290,13 @@
     <t>msr_centerhead3d_merged</t>
   </si>
   <si>
-    <r>
-      <t>centerhe3d-variant
+    <t>centerhe3d-variant
 1. shared_conv 96→64 3×3
 2. SepHead×2
-3. hm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(64→64 3×3)+final(64→4)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>；回归头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(64→64 3×3)+final(64→8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按列切</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>6.875G</t>
+3. hm头 1 hidden(64→64 3×3)+final(64→4)；回归头 1 hidden(64→64 3×3)+final(64→8 按列切)</t>
+  </si>
+  <si>
+    <t>1.751G</t>
   </si>
   <si>
     <t>0.314M</t>
@@ -441,65 +305,25 @@
     <t>msr_centerhead3d_narrow</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">centerhe3d-variant
+    <t>centerhe3d-variant
 1. shared_conv 96→32 3×3
 2. SepHead×5
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(32→32 3×3) + 1 final(32→C 3×3)</t>
-    </r>
-  </si>
-  <si>
-    <t>4.995G</t>
+3. 每头 1 hidden(32→32 3×3) + 1 final(32→C 3×3)</t>
+  </si>
+  <si>
+    <t>1.281G</t>
   </si>
   <si>
     <t>msr_centerhead3d_noconv</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">centerhe3d-variant
+    <t>centerhe3d-variant
 1. shared_conv 96→64 3×3
 2. SepHead×5
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 0 hidden + 1 final(64→C 3×3)</t>
-    </r>
-  </si>
-  <si>
-    <t>4.500G</t>
+3. 每头 0 hidden + 1 final(64→C 3×3)</t>
+  </si>
+  <si>
+    <t>1.158G</t>
   </si>
   <si>
     <t>0.240M</t>
@@ -508,51 +332,13 @@
     <t>msr_centerhead3d_trunk</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">centerhe3d-variant
+    <t>centerhe3d-variant
 1. shared_conv 96→64 3×3
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全头共用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(64→64 3×3)
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 0 hidden + 1 final(64→C 1×1)</t>
-    </r>
-  </si>
-  <si>
-    <t>5.491G</t>
+2. 全头共用 1 hidden(64→64 3×3)
+3. 每头 0 hidden + 1 final(64→C 1×1)</t>
+  </si>
+  <si>
+    <t>1.405G</t>
   </si>
   <si>
     <t>0.270M</t>
@@ -561,21 +347,7 @@
     <t>msr_radarNeXt</t>
   </si>
   <si>
-    <t>untrained</t>
-  </si>
-  <si>
-    <r>
-      <t>RadarNeXt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>原版</t>
-    </r>
+    <t>RadarNeXt原版</t>
   </si>
   <si>
     <t>PN[64]</t>
@@ -593,60 +365,22 @@
     <t>NMS[gpu,0.2]</t>
   </si>
   <si>
+    <t>4.502G</t>
+  </si>
+  <si>
     <t>1.640M</t>
   </si>
   <si>
     <t>msr_centerhead2d_k1</t>
   </si>
   <si>
-    <r>
-      <t>centerhe2d-variant
-1. shared_conv 96→64 3×3(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不受影响</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">)
+    <t>centerhe2d-variant
+1. shared_conv 96→64 3×3(不受影响)
 2. SepHead×4
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(64→64 1×1) + 1 final(64→C 1×1)</t>
-    </r>
-  </si>
-  <si>
-    <t>anchorfree2d-varant</t>
-  </si>
-  <si>
-    <t>4.856G</t>
+3. 每头 1 hidden(64→64 1×1) + 1 final(64→C 1×1)</t>
+  </si>
+  <si>
+    <t>1.247G</t>
   </si>
   <si>
     <t>0.251M</t>
@@ -655,69 +389,13 @@
     <t>msr_centerhead2d_merged</t>
   </si>
   <si>
-    <r>
-      <t>centerhe3d-variant
+    <t>centerhe3d-variant
 1. shared_conv 96→64 3×3
 2. SepHead×2
-3. hm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(64→64 3×3)+final(64→4)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>；回归头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(64→64 3×3)+final(64→6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>按列切</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>6.839G</t>
+3. hm头 1 hidden(64→64 3×3)+final(64→4)；回归头 1 hidden(64→64 3×3)+final(64→6 按列切)</t>
+  </si>
+  <si>
+    <t>1.742G</t>
   </si>
   <si>
     <t>0.313M</t>
@@ -726,33 +404,13 @@
     <t>msr_centerhead2d_narrow</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">centerhe2d-variant
+    <t>centerhe2d-variant
 1. shared_conv 96→32 3×3
 2. SepHead×4
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(32→32 3×3) + 1 final(32→C 3×3)</t>
-    </r>
-  </si>
-  <si>
-    <t>4.678G</t>
+3. 每头 1 hidden(32→32 3×3) + 1 final(32→C 3×3)</t>
+  </si>
+  <si>
+    <t>1.202G</t>
   </si>
   <si>
     <t>0.245M</t>
@@ -761,51 +419,13 @@
     <t>msr_centerhead2d_noconv</t>
   </si>
   <si>
-    <r>
-      <t>centerhe2d-variant
+    <t>centerhe2d-variant
 1. shared_conv 96→64 3×3
-2. SepHead×4(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">height)
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 0 hidden + 1 final(64→C 3×3)</t>
-    </r>
-  </si>
-  <si>
-    <t>4.463G</t>
+2. SepHead×4(无height)
+3. 每头 0 hidden + 1 final(64→C 3×3)</t>
+  </si>
+  <si>
+    <t>1.148G</t>
   </si>
   <si>
     <t>0.238M</t>
@@ -814,51 +434,13 @@
     <t>msr_centerhead2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">centerhe2d-variant
+    <t>centerhe2d-variant
 1. shared_conv 96→64 3×3
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全头共用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 1 hidden(64→64 3×3)
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每头</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 0 hidden + 1 final(64→C 1×1)</t>
-    </r>
-  </si>
-  <si>
-    <t>5.487G</t>
+2. 全头共用 1 hidden(64→64 3×3)
+3. 每头 0 hidden + 1 final(64→C 1×1)</t>
+  </si>
+  <si>
+    <t>1.404G</t>
   </si>
   <si>
     <t>msr_repdwc64_ch2d_trunk</t>
@@ -867,197 +449,52 @@
     <t>repdwc64  + centerhead2d-variant-trunk</t>
   </si>
   <si>
+    <t>anchorfree2d-varant</t>
+  </si>
+  <si>
+    <t>2.121G</t>
+  </si>
+  <si>
+    <t>0.309M</t>
+  </si>
+  <si>
     <t>msr_repdwc32_ch2d_trunk</t>
   </si>
   <si>
     <t>repdwc32  + centerhead2d-variant-trunk</t>
   </si>
   <si>
+    <t>1.036G</t>
+  </si>
+  <si>
+    <t>0.143M</t>
+  </si>
+  <si>
     <t>msr_pp64_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t>ch2d-trunk + backbone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>形态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-1. backbone PP×[64,64,64] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>通道全</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>64
+    <t>ch2d-trunk + backbone形态
+1. backbone PP×[64,64,64] 通道全64
 2. neck UPSAMPLE[1,2,4]+CONCAT[192]
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+3. head ch2d trunk（NoZ+全共享trunk）</t>
   </si>
   <si>
     <t>PP[3,5,5]*[64,64,64]</t>
   </si>
   <si>
+    <t>3.524G</t>
+  </si>
+  <si>
+    <t>0.815M</t>
+  </si>
+  <si>
     <t>msr_repdwcmix_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t>ch2d-trunk + backbone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>形态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-1. backbone RepDwc×[32,64,64] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>渐进通道</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>ch2d-trunk + backbone形态
+1. backbone RepDwc×[32,64,64] 渐进通道
 2. neck UPSAMPLE[1,2,4]+CONCAT[160]
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+3. head ch2d trunk（NoZ+全共享trunk）</t>
   </si>
   <si>
     <t>RepDwc[3,5,5]*[32,64,64]</t>
@@ -1066,797 +503,349 @@
     <t>UPSAMPLE[1,2,4]+CONCAT[160]</t>
   </si>
   <si>
+    <t>1.869G</t>
+  </si>
+  <si>
+    <t>0.276M</t>
+  </si>
+  <si>
     <t>msr_ppmix_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t>ch2d-trunk + backbone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>形态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-1. backbone PP×[32,64,64] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>渐进通道</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>ch2d-trunk + backbone形态
+1. backbone PP×[32,64,64] 渐进通道
 2. neck UPSAMPLE[1,2,4]+CONCAT[160]
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+3. head ch2d trunk（NoZ+全共享trunk）</t>
   </si>
   <si>
     <t>PP[3,5,5]*[32,64,64]</t>
   </si>
   <si>
+    <t>2.573G</t>
+  </si>
+  <si>
+    <t>0.683M</t>
+  </si>
+  <si>
     <t>msr_pp553_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t>ch2d-trunk + backbone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>形态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-1. backbone PP×[5,5,3] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层数重心前移</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>ch2d-trunk + backbone形态
+1. backbone PP×[5,5,3] 层数重心前移
 2. neck UPSAMPLE[1,2,4]+CONCAT[96]
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+3. head ch2d trunk（NoZ+全共享trunk）</t>
   </si>
   <si>
     <t>PP[5,5,3]*[32,32,32]</t>
   </si>
   <si>
+    <t>1.544G</t>
+  </si>
+  <si>
     <t>msr_pp_strides_122_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t>ch2d-trunk + backbone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>形态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-1. backbone PP×[32,32,32]@s[1,2,2] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>首级不下采保</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>x</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>亚格子分辨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-2. neck UPSAMPLE[1,1,2]+CONCAT[96] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>适配两级下采</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <t>PP[3,5,5]*[32,32,32]@s[1,2,2]</t>
-  </si>
-  <si>
-    <t>UPSAMPLE[1,1,2]+CONCAT[96]</t>
+    <t>ch2d-trunk + backbone形态
+1. backbone PP×[32,32,32]@s[1,2,2] 首级不下采保x亚格子分辨
+2. neck UPSAMPLE[1,1,2]+CONCAT[96] 适配两级下采
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>UPSAMPLE[0.5,1,2]+CONCAT[96]</t>
+  </si>
+  <si>
+    <t>2.623G</t>
+  </si>
+  <si>
+    <t>0.258M</t>
   </si>
   <si>
     <t>msr_repdwc64_mdfen_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">ch2d-trunk + MDFEN neck
-1. backbone RepDwc×[64,64,64] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>通道全</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">64
-2. neck MDFEN[192] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>独立多尺度融合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+    <t>ch2d-trunk + MDFEN neck
+1. backbone RepDwc×[64,64,64] 通道全64
+2. neck MDFEN[192] 独立多尺度融合
+3. head ch2d trunk（NoZ+全共享trunk）</t>
   </si>
   <si>
     <t>MDFEN[192]</t>
   </si>
   <si>
+    <t>1.800G</t>
+  </si>
+  <si>
+    <t>0.793M</t>
+  </si>
+  <si>
     <t>msr_repdwc64_mdfen_pn64_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t>ch2d-trunk + MDFEN + VFE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>升</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>64
-1. VFE PN[64]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>32→64</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>ch2d-trunk + MDFEN + VFE升64
+1. VFE PN[64]（32→64）
 2. backbone RepDwc×[64,64,64]; neck MDFEN[192]
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>1.843G</t>
+  </si>
+  <si>
+    <t>0.796M</t>
   </si>
   <si>
     <t>msr_repdwc32_mdfen_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">ch2d-trunk + MDFEN neck
-1. backbone RepDwc×[32,32,32] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>通道默认</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>ch2d-trunk + MDFEN neck
+1. backbone RepDwc×[32,32,32] 通道默认
 2. neck MDFEN[96]
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+3. head ch2d trunk（NoZ+全共享trunk）</t>
   </si>
   <si>
     <t>MDFEN[96]</t>
   </si>
   <si>
+    <t>0.660G</t>
+  </si>
+  <si>
+    <t>0.272M</t>
+  </si>
+  <si>
     <t>msr_repdwcmix_mdfen_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">ch2d-trunk + MDFEN neck
-1. backbone RepDwc×[32,64,64] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>渐进通道</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>ch2d-trunk + MDFEN neck
+1. backbone RepDwc×[32,64,64] 渐进通道
 2. neck MDFEN[160]
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+3. head ch2d trunk（NoZ+全共享trunk）</t>
   </si>
   <si>
     <t>MDFEN[160]</t>
   </si>
   <si>
+    <t>0.822G</t>
+  </si>
+  <si>
+    <t>0.366M</t>
+  </si>
+  <si>
     <t>msr_repdwc32_mdfen_pn64_ch2d_trunk</t>
   </si>
   <si>
-    <r>
-      <t>ch2d-trunk + MDFEN + VFE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>升</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>64
-1. VFE PN[64]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>32→64</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>ch2d-trunk + MDFEN + VFE升64
+1. VFE PN[64]（32→64）
 2. backbone RepDwc×[32,32,32]; neck MDFEN[96]
-3. head ch2d trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>NoZ+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全共享</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>trunk</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>0.703G</t>
+  </si>
+  <si>
+    <t>0.275M</t>
+  </si>
+  <si>
+    <t>msr_pp333mix_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态
+1. backbone PP×[3,3,3] 层数均3 + 渐进通道[32,64,64]
+2. neck UPSAMPLE[1,2,4]+CONCAT[160]
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>PP[3,3,3]*[32,64,64]</t>
+  </si>
+  <si>
+    <t>anchorfree-trunk</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.2,mc]</t>
+  </si>
+  <si>
+    <t>2.387G</t>
+  </si>
+  <si>
+    <t>0.535M</t>
+  </si>
+  <si>
+    <t>msr_pp333mix_pn64_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态 + VFE升64
+1. VFE PN[64]（32→64）
+2. backbone PP×[3,3,3] 层数均3 + 渐进通道[32,64,64]; neck UPSAMPLE[1,2,4]+CONCAT[160]
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.3,mc]</t>
+  </si>
+  <si>
+    <t>2.430G</t>
+  </si>
+  <si>
+    <t>0.537M</t>
+  </si>
+  <si>
+    <t>msr_ppmixrev_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态
+1. backbone PP×[3,5,5] 通道递减[64,32,32]
+2. neck UPSAMPLE[1,2,4]+CONCAT[128]
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>PP[3,5,5]*[64,32,32]</t>
+  </si>
+  <si>
+    <t>UPSAMPLE[1,2,4]+CONCAT[128]</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.4,mc]</t>
+  </si>
+  <si>
+    <t>2.337G</t>
+  </si>
+  <si>
+    <t>0.394M</t>
+  </si>
+  <si>
+    <t>msr_ppmixrev_pn64_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态 + VFE升64
+1. VFE PN[64]（32→64）
+2. backbone PP×[3,5,5] 通道递减[64,32,32]; neck UPSAMPLE[1,2,4]+CONCAT[128]
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.5,mc]</t>
+  </si>
+  <si>
+    <t>2.380G</t>
+  </si>
+  <si>
+    <t>0.396M</t>
+  </si>
+  <si>
+    <t>msr_pp2s6432_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态
+1. backbone PP×[3,6] 两级递减通道[64,32]
+2. neck UPSAMPLE[1,2]+CONCAT[96] 适配两级下采
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>PP[3,6]*[64,32]</t>
+  </si>
+  <si>
+    <t>UPSAMPLE[1,2]+CONCAT[96]</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.6,mc]</t>
+  </si>
+  <si>
+    <t>2.048G</t>
+  </si>
+  <si>
+    <t>0.312M</t>
+  </si>
+  <si>
+    <t>msr_pp2s6432_pn64_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态 + VFE升64
+1. VFE PN[64]（32→64）
+2. backbone PP×[3,6] 两级递减通道[64,32]; neck UPSAMPLE[1,2]+CONCAT[96]
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.7,mc]</t>
+  </si>
+  <si>
+    <t>2.091G</t>
+  </si>
+  <si>
+    <t>0.315M</t>
+  </si>
+  <si>
+    <t>msr_pp2s32_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态
+1. backbone PP×[3,5] 两级等通道[32,32]
+2. neck UPSAMPLE[1,2]+CONCAT[64] 适配两级下采
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>PP[3,5]*[32,32]</t>
+  </si>
+  <si>
+    <t>UPSAMPLE[1,2]+CONCAT[64]</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.8,mc]</t>
+  </si>
+  <si>
+    <t>1.097G</t>
+  </si>
+  <si>
+    <t>msr_pp2s32_pn64_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态 + VFE升64
+1. VFE PN[64]（32→64）
+2. backbone PP×[3,5] 两级等通道[32,32]; neck UPSAMPLE[1,2]+CONCAT[64]
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.9,mc]</t>
+  </si>
+  <si>
+    <t>1.140G</t>
+  </si>
+  <si>
+    <t>0.182M</t>
+  </si>
+  <si>
+    <t>msr_pp2smix_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态
+1. backbone PP×[3,5] 两级渐进通道[32,64]
+2. neck UPSAMPLE[1,2]+CONCAT[96] 适配两级下采
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>PP[3,5]*[32,64]</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.10,mc]</t>
+  </si>
+  <si>
+    <t>1.640G</t>
+  </si>
+  <si>
+    <t>0.358M</t>
+  </si>
+  <si>
+    <t>msr_pp2smix_pn64_ch2d_trunk</t>
+  </si>
+  <si>
+    <t>ch2d-trunk + backbone形态 + VFE升64
+1. VFE PN[64]（32→64）
+2. backbone PP×[3,5] 两级渐进通道[32,64]; neck UPSAMPLE[1,2]+CONCAT[96]
+3. head ch2d trunk（NoZ+全共享trunk）</t>
+  </si>
+  <si>
+    <t>NMS[gpu,0.11,mc]</t>
+  </si>
+  <si>
+    <t>1.683G</t>
+  </si>
+  <si>
+    <t>0.361M</t>
   </si>
 </sst>
 </file>
@@ -1869,7 +858,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1893,7 +882,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1901,7 +890,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2035,18 +1024,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2086,6 +1069,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2448,13 +1443,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -2478,16 +1473,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="10">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
@@ -2496,89 +1491,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2609,16 +1604,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2628,7 +1620,13 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2940,7 +1938,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.125" style="4" customWidth="1"/>
@@ -3013,7 +2011,7 @@
       <c r="N1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="9"/>
+      <c r="O1" s="10"/>
       <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
@@ -3059,7 +2057,7 @@
       <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="11"/>
@@ -3137,7 +2135,7 @@
       <c r="B3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="11"/>
@@ -3156,7 +2154,7 @@
       <c r="I3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="13" t="s">
         <v>39</v>
       </c>
       <c r="K3" s="3" t="s">
@@ -3215,7 +2213,7 @@
       <c r="B4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D4" s="11"/>
@@ -3234,7 +2232,7 @@
       <c r="I4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>44</v>
       </c>
       <c r="K4" s="3" t="s">
@@ -3293,7 +2291,7 @@
       <c r="B5" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="11"/>
@@ -3303,7 +2301,7 @@
       <c r="F5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="13" t="s">
         <v>49</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -3320,14 +2318,14 @@
       </c>
       <c r="L5" s="11"/>
       <c r="M5" s="3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="O5" s="11"/>
       <c r="P5" s="3">
-        <v>82.34</v>
+        <v>82.35</v>
       </c>
       <c r="Q5" s="3">
         <v>93.01</v>
@@ -3366,13 +2364,13 @@
     </row>
     <row r="6" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>52</v>
+      <c r="C6" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="3" t="s">
@@ -3384,8 +2382,8 @@
       <c r="G6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>53</v>
+      <c r="H6" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>31</v>
@@ -3398,10 +2396,10 @@
       </c>
       <c r="L6" s="11"/>
       <c r="M6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="O6" s="11"/>
       <c r="P6" s="3">
@@ -3444,13 +2442,13 @@
     </row>
     <row r="7" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>57</v>
+      <c r="C7" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="3" t="s">
@@ -3462,11 +2460,11 @@
       <c r="G7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>32</v>
@@ -3476,10 +2474,10 @@
       </c>
       <c r="L7" s="11"/>
       <c r="M7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="O7" s="11"/>
       <c r="P7" s="3">
@@ -3522,13 +2520,13 @@
     </row>
     <row r="8" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A8" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>63</v>
+      <c r="C8" s="14" t="s">
+        <v>62</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="3" t="s">
@@ -3546,18 +2544,18 @@
       <c r="I8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="14" t="s">
-        <v>64</v>
+      <c r="J8" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L8" s="11"/>
       <c r="M8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="3">
@@ -3595,13 +2593,13 @@
     </row>
     <row r="9" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A9" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>68</v>
+      <c r="C9" s="14" t="s">
+        <v>67</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="3" t="s">
@@ -3619,18 +2617,18 @@
       <c r="I9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="14" t="s">
-        <v>64</v>
+      <c r="J9" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L9" s="11"/>
       <c r="M9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="O9" s="11"/>
       <c r="P9" s="3">
@@ -3651,7 +2649,7 @@
       <c r="U9" s="3"/>
       <c r="V9" s="11"/>
       <c r="W9" s="3">
-        <v>90.75</v>
+        <v>90.74</v>
       </c>
       <c r="X9" s="3">
         <v>95.89</v>
@@ -3668,13 +2666,13 @@
     </row>
     <row r="10" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A10" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>72</v>
+      <c r="C10" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="3" t="s">
@@ -3692,18 +2690,18 @@
       <c r="I10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="14" t="s">
-        <v>64</v>
+      <c r="J10" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L10" s="11"/>
       <c r="M10" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O10" s="11"/>
       <c r="P10" s="3">
@@ -3741,13 +2739,13 @@
     </row>
     <row r="11" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>75</v>
+      <c r="C11" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="3" t="s">
@@ -3765,18 +2763,18 @@
       <c r="I11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J11" s="14" t="s">
-        <v>64</v>
+      <c r="J11" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L11" s="11"/>
       <c r="M11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="3">
@@ -3814,13 +2812,13 @@
     </row>
     <row r="12" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>79</v>
+      <c r="C12" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="3" t="s">
@@ -3838,18 +2836,18 @@
       <c r="I12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="14" t="s">
-        <v>64</v>
+      <c r="J12" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L12" s="11"/>
       <c r="M12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="O12" s="11"/>
       <c r="P12" s="3">
@@ -3887,65 +2885,87 @@
     </row>
     <row r="13" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>39</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="11"/>
+      <c r="M13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L13" s="11"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
+      <c r="P13" s="2">
+        <v>92.1</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>94.1</v>
+      </c>
+      <c r="R13" s="2">
+        <v>76.15</v>
+      </c>
+      <c r="S13" s="2">
+        <v>98.46</v>
+      </c>
+      <c r="T13" s="2">
+        <v>99.69</v>
+      </c>
       <c r="U13" s="2"/>
       <c r="V13" s="11"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
+      <c r="W13" s="2">
+        <v>91.82</v>
+      </c>
+      <c r="X13" s="2">
+        <v>94.1</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>98.48</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>98.71</v>
+      </c>
       <c r="AB13" s="2"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>92</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="3" t="s">
@@ -3963,37 +2983,62 @@
       <c r="I14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="14" t="s">
-        <v>93</v>
+      <c r="J14" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L14" s="11"/>
       <c r="M14" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
+      <c r="P14" s="3">
+        <v>89.22</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>95.98</v>
+      </c>
+      <c r="R14" s="3">
+        <v>64.08</v>
+      </c>
+      <c r="S14" s="3">
+        <v>97.17</v>
+      </c>
+      <c r="T14" s="3">
+        <v>99.64</v>
+      </c>
       <c r="U14" s="3"/>
       <c r="V14" s="11"/>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>97</v>
+        <v>94</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="3" t="s">
@@ -4011,37 +3056,62 @@
       <c r="I15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="14" t="s">
-        <v>93</v>
+      <c r="J15" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L15" s="11"/>
       <c r="M15" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O15" s="11"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
+      <c r="P15" s="3">
+        <v>90.7</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>95.9</v>
+      </c>
+      <c r="R15" s="3">
+        <v>69.97</v>
+      </c>
+      <c r="S15" s="3">
+        <v>97.25</v>
+      </c>
+      <c r="T15" s="3">
+        <v>99.68</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="11"/>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" s="3" customFormat="1" ht="18" customHeight="1" spans="1:28">
       <c r="A16" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="3" t="s">
@@ -4059,37 +3129,62 @@
       <c r="I16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="14" t="s">
-        <v>93</v>
+      <c r="J16" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L16" s="11"/>
       <c r="M16" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O16" s="11"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
+      <c r="P16" s="3">
+        <v>90.38</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>98.74</v>
+      </c>
+      <c r="R16" s="3">
+        <v>65.83</v>
+      </c>
+      <c r="S16" s="3">
+        <v>97.25</v>
+      </c>
+      <c r="T16" s="3">
+        <v>99.7</v>
+      </c>
       <c r="U16" s="3"/>
       <c r="V16" s="11"/>
+      <c r="W16" s="3">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
+    <row r="17" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
       <c r="A17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>103</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="3" t="s">
@@ -4107,37 +3202,62 @@
       <c r="I17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J17" s="14" t="s">
-        <v>93</v>
+      <c r="J17" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L17" s="11"/>
       <c r="M17" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O17" s="11"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
+      <c r="P17" s="3">
+        <v>89.64</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>96.23</v>
+      </c>
+      <c r="R17" s="3">
+        <v>65.42</v>
+      </c>
+      <c r="S17" s="3">
+        <v>97.21</v>
+      </c>
+      <c r="T17" s="3">
+        <v>99.72</v>
+      </c>
       <c r="U17" s="3"/>
       <c r="V17" s="11"/>
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
+    <row r="18" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
       <c r="A18" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="3" t="s">
@@ -4155,37 +3275,62 @@
       <c r="I18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="14" t="s">
-        <v>93</v>
+      <c r="J18" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L18" s="11"/>
-      <c r="M18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>81</v>
+      <c r="M18" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="N18" s="16" t="s">
+        <v>80</v>
       </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
+      <c r="P18" s="16">
+        <v>90.26</v>
+      </c>
+      <c r="Q18" s="16">
+        <v>96.25</v>
+      </c>
+      <c r="R18" s="16">
+        <v>67.94</v>
+      </c>
+      <c r="S18" s="16">
+        <v>97.11</v>
+      </c>
+      <c r="T18" s="16">
+        <v>99.76</v>
+      </c>
       <c r="U18" s="3"/>
       <c r="V18" s="11"/>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
+    <row r="19" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
       <c r="A19" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>83</v>
+        <v>109</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="3" t="s">
@@ -4197,39 +3342,68 @@
       <c r="G19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="I19" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>93</v>
+      <c r="J19" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L19" s="11"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
+      <c r="M19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="O19" s="11"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
+      <c r="P19" s="3">
+        <v>90.4</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>96.69</v>
+      </c>
+      <c r="R19" s="3">
+        <v>67.93</v>
+      </c>
+      <c r="S19" s="3">
+        <v>97.2</v>
+      </c>
+      <c r="T19" s="3">
+        <v>99.76</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="11"/>
+      <c r="W19" s="3">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
+    <row r="20" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
       <c r="A20" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>83</v>
+        <v>114</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="3" t="s">
@@ -4241,39 +3415,68 @@
       <c r="G20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20" s="14" t="s">
+      <c r="H20" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J20" s="14" t="s">
-        <v>93</v>
+      <c r="J20" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L20" s="11"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
+      <c r="M20" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="O20" s="11"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
+      <c r="P20" s="3">
+        <v>86.32</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>95.39</v>
+      </c>
+      <c r="R20" s="3">
+        <v>55.77</v>
+      </c>
+      <c r="S20" s="3">
+        <v>97.05</v>
+      </c>
+      <c r="T20" s="3">
+        <v>97.05</v>
+      </c>
       <c r="U20" s="3"/>
       <c r="V20" s="11"/>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
+    <row r="21" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
       <c r="A21" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>119</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="3" t="s">
@@ -4285,39 +3488,68 @@
       <c r="G21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="J21" s="14" t="s">
-        <v>93</v>
+      <c r="H21" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L21" s="11"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
+      <c r="M21" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>122</v>
+      </c>
       <c r="O21" s="11"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
+      <c r="P21" s="16">
+        <v>92.93</v>
+      </c>
+      <c r="Q21" s="16">
+        <v>98.95</v>
+      </c>
+      <c r="R21" s="16">
+        <v>73.2</v>
+      </c>
+      <c r="S21" s="16">
+        <v>99.7</v>
+      </c>
+      <c r="T21" s="16">
+        <v>99.88</v>
+      </c>
       <c r="U21" s="3"/>
       <c r="V21" s="11"/>
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
+    <row r="22" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
       <c r="A22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>119</v>
+        <v>123</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="3" t="s">
@@ -4329,39 +3561,68 @@
       <c r="G22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>93</v>
+      <c r="H22" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L22" s="11"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+      <c r="M22" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="O22" s="11"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
+      <c r="P22" s="3">
+        <v>89.21</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>95.98</v>
+      </c>
+      <c r="R22" s="3">
+        <v>64.02</v>
+      </c>
+      <c r="S22" s="3">
+        <v>97.11</v>
+      </c>
+      <c r="T22" s="3">
+        <v>99.73</v>
+      </c>
       <c r="U22" s="3"/>
       <c r="V22" s="11"/>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
+    <row r="23" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
       <c r="A23" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>123</v>
+        <v>129</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>130</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="3" t="s">
@@ -4373,39 +3634,68 @@
       <c r="G23" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H23" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>93</v>
+      <c r="H23" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L23" s="11"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
+      <c r="M23" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>133</v>
+      </c>
       <c r="O23" s="11"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
+      <c r="P23" s="17">
+        <v>92.29</v>
+      </c>
+      <c r="Q23" s="17">
+        <v>98.78</v>
+      </c>
+      <c r="R23" s="17">
+        <v>70.88</v>
+      </c>
+      <c r="S23" s="17">
+        <v>99.65</v>
+      </c>
+      <c r="T23" s="17">
+        <v>99.84</v>
+      </c>
       <c r="U23" s="3"/>
       <c r="V23" s="11"/>
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
+    <row r="24" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
       <c r="A24" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>126</v>
+        <v>134</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="3" t="s">
@@ -4417,39 +3707,68 @@
       <c r="G24" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H24" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="H24" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J24" s="14" t="s">
-        <v>93</v>
+      <c r="J24" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L24" s="11"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+      <c r="M24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="O24" s="11"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
+      <c r="P24" s="3">
+        <v>90.44</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>96.25</v>
+      </c>
+      <c r="R24" s="3">
+        <v>68.52</v>
+      </c>
+      <c r="S24" s="3">
+        <v>97.25</v>
+      </c>
+      <c r="T24" s="3">
+        <v>99.75</v>
+      </c>
       <c r="U24" s="3"/>
       <c r="V24" s="11"/>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
+    <row r="25" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
       <c r="A25" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>129</v>
+        <v>138</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="3" t="s">
@@ -4461,39 +3780,68 @@
       <c r="G25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>93</v>
+      <c r="H25" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L25" s="11"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
+      <c r="M25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="O25" s="11"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
+      <c r="P25" s="3">
+        <v>90.02</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>95.78</v>
+      </c>
+      <c r="R25" s="3">
+        <v>67.37</v>
+      </c>
+      <c r="S25" s="3">
+        <v>97.16</v>
+      </c>
+      <c r="T25" s="3">
+        <v>99.75</v>
+      </c>
       <c r="U25" s="3"/>
       <c r="V25" s="11"/>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
-      <c r="A26" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>133</v>
+    <row r="26" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
+      <c r="A26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="3" t="s">
@@ -4505,67 +3853,139 @@
       <c r="G26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>93</v>
+      <c r="H26" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L26" s="11"/>
+      <c r="M26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>147</v>
+      </c>
       <c r="O26" s="11"/>
+      <c r="P26" s="3">
+        <v>89.21</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>95.89</v>
+      </c>
+      <c r="R26" s="3">
+        <v>62.8</v>
+      </c>
+      <c r="S26" s="3">
+        <v>98.4</v>
+      </c>
+      <c r="T26" s="3">
+        <v>99.73</v>
+      </c>
       <c r="V26" s="11"/>
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
-      <c r="A27" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>136</v>
+    <row r="27" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
+      <c r="A27" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="14" t="s">
-        <v>85</v>
+      <c r="F27" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="14" t="s">
-        <v>93</v>
+      <c r="H27" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L27" s="11"/>
+      <c r="M27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="O27" s="11"/>
+      <c r="P27" s="3">
+        <v>86.71</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>90.74</v>
+      </c>
+      <c r="R27" s="3">
+        <v>60.25</v>
+      </c>
+      <c r="S27" s="3">
+        <v>96.33</v>
+      </c>
+      <c r="T27" s="3">
+        <v>99.52</v>
+      </c>
       <c r="V27" s="11"/>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
-      <c r="A28" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>138</v>
+    <row r="28" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
+      <c r="A28" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>153</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="3" t="s">
@@ -4577,31 +3997,67 @@
       <c r="G28" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H28" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>93</v>
+      <c r="H28" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L28" s="11"/>
+      <c r="M28" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="O28" s="11"/>
+      <c r="P28" s="3">
+        <v>86.05</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>96.28</v>
+      </c>
+      <c r="R28" s="3">
+        <v>54.66</v>
+      </c>
+      <c r="S28" s="3">
+        <v>96.08</v>
+      </c>
+      <c r="T28" s="3">
+        <v>97.17</v>
+      </c>
       <c r="V28" s="11"/>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
-      <c r="A29" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>141</v>
+    <row r="29" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
+      <c r="A29" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>158</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="3" t="s">
@@ -4613,59 +4069,824 @@
       <c r="G29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H29" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>93</v>
+      <c r="H29" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L29" s="11"/>
+      <c r="M29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="O29" s="11"/>
+      <c r="P29" s="3">
+        <v>86.33</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>96.02</v>
+      </c>
+      <c r="R29" s="3">
+        <v>56.26</v>
+      </c>
+      <c r="S29" s="3">
+        <v>96.12</v>
+      </c>
+      <c r="T29" s="3">
+        <v>96.91</v>
+      </c>
       <c r="V29" s="11"/>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" s="3" customFormat="1" ht="18" customHeight="1" spans="1:22">
-      <c r="A30" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" s="17"/>
+    <row r="30" s="3" customFormat="1" ht="18" customHeight="1" spans="1:27">
+      <c r="A30" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="18"/>
       <c r="E30" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="14" t="s">
-        <v>85</v>
+      <c r="F30" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>93</v>
+      <c r="H30" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L30" s="11"/>
+      <c r="M30" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>165</v>
+      </c>
       <c r="O30" s="11"/>
-      <c r="V30" s="17"/>
+      <c r="P30" s="3">
+        <v>84.96</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>90.76</v>
+      </c>
+      <c r="R30" s="3">
+        <v>55.98</v>
+      </c>
+      <c r="S30" s="3">
+        <v>96.03</v>
+      </c>
+      <c r="T30" s="3">
+        <v>97.07</v>
+      </c>
+      <c r="V30" s="18"/>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:27">
+      <c r="A31" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="P31" s="3">
+        <v>91.61</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>96.32</v>
+      </c>
+      <c r="R31" s="3">
+        <v>70.91</v>
+      </c>
+      <c r="S31" s="3">
+        <v>99.45</v>
+      </c>
+      <c r="T31" s="3">
+        <v>99.76</v>
+      </c>
+      <c r="U31" s="3"/>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:27">
+      <c r="A32" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="P32" s="3">
+        <v>89.04</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>89.9</v>
+      </c>
+      <c r="R32" s="3">
+        <v>69.43</v>
+      </c>
+      <c r="S32" s="3">
+        <v>97.19</v>
+      </c>
+      <c r="T32" s="3">
+        <v>99.64</v>
+      </c>
+      <c r="U32" s="3"/>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:27">
+      <c r="A33" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="P33" s="3">
+        <v>90.65</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>96.11</v>
+      </c>
+      <c r="R33" s="3">
+        <v>69.55</v>
+      </c>
+      <c r="S33" s="3">
+        <v>97.2</v>
+      </c>
+      <c r="T33" s="3">
+        <v>99.75</v>
+      </c>
+      <c r="U33" s="3"/>
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:27">
+      <c r="A34" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P34" s="3">
+        <v>91.9</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>98.56</v>
+      </c>
+      <c r="R34" s="3">
+        <v>69.63</v>
+      </c>
+      <c r="S34" s="3">
+        <v>99.58</v>
+      </c>
+      <c r="T34" s="3">
+        <v>99.82</v>
+      </c>
+      <c r="U34" s="3"/>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:27">
+      <c r="A35" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="P35" s="3">
+        <v>90.11</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>95.2</v>
+      </c>
+      <c r="R35" s="3">
+        <v>68.36</v>
+      </c>
+      <c r="S35" s="3">
+        <v>97.12</v>
+      </c>
+      <c r="T35" s="3">
+        <v>99.75</v>
+      </c>
+      <c r="U35" s="3"/>
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:27">
+      <c r="A36" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="P36" s="3">
+        <v>90.43</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>96.05</v>
+      </c>
+      <c r="R36" s="3">
+        <v>68.71</v>
+      </c>
+      <c r="S36" s="3">
+        <v>97.16</v>
+      </c>
+      <c r="T36" s="3">
+        <v>99.81</v>
+      </c>
+      <c r="U36" s="3"/>
+      <c r="W36" s="3">
+        <v>0</v>
+      </c>
+      <c r="X36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:27">
+      <c r="A37" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P37" s="3">
+        <v>88.17</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>95.25</v>
+      </c>
+      <c r="R37" s="3">
+        <v>63.17</v>
+      </c>
+      <c r="S37" s="3">
+        <v>97.04</v>
+      </c>
+      <c r="T37" s="3">
+        <v>97.21</v>
+      </c>
+      <c r="U37" s="3"/>
+      <c r="W37" s="3">
+        <v>0</v>
+      </c>
+      <c r="X37" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:27">
+      <c r="A38" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="P38" s="3">
+        <v>87.43</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>96.05</v>
+      </c>
+      <c r="R38" s="3">
+        <v>59.34</v>
+      </c>
+      <c r="S38" s="3">
+        <v>97.05</v>
+      </c>
+      <c r="T38" s="3">
+        <v>97.26</v>
+      </c>
+      <c r="U38" s="3"/>
+      <c r="W38" s="3">
+        <v>0</v>
+      </c>
+      <c r="X38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:27">
+      <c r="A39" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="P39" s="3">
+        <v>90.23</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>95.82</v>
+      </c>
+      <c r="R39" s="3">
+        <v>68.3</v>
+      </c>
+      <c r="S39" s="3">
+        <v>97.14</v>
+      </c>
+      <c r="T39" s="3">
+        <v>99.66</v>
+      </c>
+      <c r="U39" s="3"/>
+      <c r="W39" s="3">
+        <v>0</v>
+      </c>
+      <c r="X39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:27">
+      <c r="A40" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="P40" s="3">
+        <v>90.41</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>96.65</v>
+      </c>
+      <c r="R40" s="3">
+        <v>67.98</v>
+      </c>
+      <c r="S40" s="3">
+        <v>97.21</v>
+      </c>
+      <c r="T40" s="3">
+        <v>99.8</v>
+      </c>
+      <c r="U40" s="3"/>
+      <c r="W40" s="3">
+        <v>0</v>
+      </c>
+      <c r="X40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="E1:K40" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="D1:D30"/>
     <mergeCell ref="L1:L30"/>
